--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_20-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_20-10-2025.xlsx
@@ -538,17 +538,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£9.95</t>
+          <t>£9.93</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£9.95</t>
+          <t>£9.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£9.95</t>
+          <t>£9.93</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£10.03</t>
+          <t>£10.02</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -780,17 +780,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£14.55</t>
+          <t>£14.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£14.55</t>
+          <t>£14.50</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£14.55</t>
+          <t>£14.50</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£14.64</t>
+          <t>£14.63</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£14.85</t>
+          <t>£14.78</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£14.85</t>
+          <t>£14.78</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£14.85</t>
+          <t>£14.78</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£14.93</t>
+          <t>£14.92</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£18.90</t>
+          <t>£18.80</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£18.90</t>
+          <t>£18.80</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£18.90</t>
+          <t>£18.80</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1143,17 +1143,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£20.70</t>
+          <t>£20.50</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£20.70</t>
+          <t>£20.50</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£20.70</t>
+          <t>£20.50</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£23.90</t>
+          <t>£23.75</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£23.90</t>
+          <t>£23.75</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£23.90</t>
+          <t>£23.75</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1506,17 +1506,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£25.90</t>
+          <t>£25.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£25.90</t>
+          <t>£25.75</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£25.90</t>
+          <t>£25.75</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1627,17 +1627,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£25.55</t>
+          <t>£25.40</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£25.55</t>
+          <t>£25.40</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£25.55</t>
+          <t>£25.40</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1869,17 +1869,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£31.40</t>
+          <t>£31.10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£31.40</t>
+          <t>£31.10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£31.40</t>
+          <t>£31.10</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£38.80</t>
+          <t>£38.63</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£38.80</t>
+          <t>£38.63</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2232,17 +2232,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£38.25</t>
+          <t>£38.10</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£38.25</t>
+          <t>£38.10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£38.25</t>
+          <t>£38.10</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
